--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233984</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137235288</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137231203</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137233141</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137261938</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137229409</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137230592</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137231226</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137231410</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137233160</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137235031</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137235205</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137254773</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137254774</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137232286</v>
       </c>
       <c r="B17" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137234103</v>
       </c>
       <c r="B18" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137233947</v>
       </c>
       <c r="B19" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137234938</v>
       </c>
       <c r="B22" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>137254772</v>
       </c>
       <c r="B24" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137229198</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>137229611</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137229946</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137230226</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137230276</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137230372</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137231296</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137231398</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137231488</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137232819</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137232846</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137233192</v>
       </c>
       <c r="B37" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137233573</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137233676</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>137261670</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>137261705</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137262560</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>137262737</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137262883</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>137262978</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>137263018</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>137264116</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137263281</v>
       </c>
       <c r="B48" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>137229855</v>
       </c>
       <c r="B55" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137231784</v>
       </c>
       <c r="B56" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137232326</v>
       </c>
       <c r="B57" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>137232603</v>
       </c>
       <c r="B58" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>137254781</v>
       </c>
       <c r="B59" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>137254782</v>
       </c>
       <c r="B60" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137263199</v>
       </c>
       <c r="B61" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137229897</v>
       </c>
       <c r="B62" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>137233252</v>
       </c>
       <c r="B63" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137234449</v>
       </c>
       <c r="B64" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>137254778</v>
       </c>
       <c r="B65" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>137234122</v>
       </c>
       <c r="B67" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>137262332</v>
       </c>
       <c r="B68" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137232378</v>
       </c>
       <c r="B69" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>137230795</v>
       </c>
       <c r="B70" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>137229268</v>
       </c>
       <c r="B77" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>137231851</v>
       </c>
       <c r="B78" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>137229679</v>
       </c>
       <c r="B80" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>137231352</v>
       </c>
       <c r="B87" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137231958</v>
       </c>
       <c r="B88" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>137232435</v>
       </c>
       <c r="B89" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>137232467</v>
       </c>
       <c r="B90" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>137263435</v>
       </c>
       <c r="B91" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>137263830</v>
       </c>
       <c r="B92" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>137233307</v>
       </c>
       <c r="B93" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137254789</v>
       </c>
       <c r="B95" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233984</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137235288</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137231203</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137233141</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137261938</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137229409</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137230592</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137231226</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137231410</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137233160</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137235031</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137235205</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137254773</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137254774</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137232286</v>
       </c>
       <c r="B17" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137234103</v>
       </c>
       <c r="B18" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137233947</v>
       </c>
       <c r="B19" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137234938</v>
       </c>
       <c r="B22" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>137254772</v>
       </c>
       <c r="B24" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137229198</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>137229611</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137229946</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137230226</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137230276</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137230372</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137231296</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137231398</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137231488</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137232819</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137232846</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137233192</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137233573</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137233676</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>137261670</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>137261705</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137262560</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>137262737</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137262883</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>137262978</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>137263018</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>137264116</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137263281</v>
       </c>
       <c r="B48" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>137229855</v>
       </c>
       <c r="B55" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137231784</v>
       </c>
       <c r="B56" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137232326</v>
       </c>
       <c r="B57" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>137232603</v>
       </c>
       <c r="B58" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>137254781</v>
       </c>
       <c r="B59" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>137254782</v>
       </c>
       <c r="B60" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137263199</v>
       </c>
       <c r="B61" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137229897</v>
       </c>
       <c r="B62" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>137233252</v>
       </c>
       <c r="B63" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137234449</v>
       </c>
       <c r="B64" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>137254778</v>
       </c>
       <c r="B65" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>137234122</v>
       </c>
       <c r="B67" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>137262332</v>
       </c>
       <c r="B68" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137232378</v>
       </c>
       <c r="B69" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>137231352</v>
       </c>
       <c r="B87" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137231958</v>
       </c>
       <c r="B88" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>137232435</v>
       </c>
       <c r="B89" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>137232467</v>
       </c>
       <c r="B90" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>137263435</v>
       </c>
       <c r="B91" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>137263830</v>
       </c>
       <c r="B92" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>137233307</v>
       </c>
       <c r="B93" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137254789</v>
       </c>
       <c r="B95" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233984</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137235288</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137231203</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137233141</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137261938</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137229409</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137230592</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137231226</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137231410</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137233160</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137235031</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137235205</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137254773</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137254774</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137232286</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137234103</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137233947</v>
       </c>
       <c r="B19" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137234938</v>
       </c>
       <c r="B22" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>137254772</v>
       </c>
       <c r="B24" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137229198</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>137229611</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137229946</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137230226</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137230276</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137230372</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137231296</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137231398</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137231488</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137232819</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137232846</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137233192</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137233573</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137233676</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>137261670</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>137261705</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137262560</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>137262737</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137262883</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>137262978</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>137263018</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>137264116</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137263281</v>
       </c>
       <c r="B48" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>137229855</v>
       </c>
       <c r="B55" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137231784</v>
       </c>
       <c r="B56" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137232326</v>
       </c>
       <c r="B57" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>137232603</v>
       </c>
       <c r="B58" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>137254781</v>
       </c>
       <c r="B59" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>137254782</v>
       </c>
       <c r="B60" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137263199</v>
       </c>
       <c r="B61" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137229897</v>
       </c>
       <c r="B62" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>137233252</v>
       </c>
       <c r="B63" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137234449</v>
       </c>
       <c r="B64" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>137254778</v>
       </c>
       <c r="B65" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>137234122</v>
       </c>
       <c r="B67" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>137262332</v>
       </c>
       <c r="B68" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137232378</v>
       </c>
       <c r="B69" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>137231352</v>
       </c>
       <c r="B87" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137231958</v>
       </c>
       <c r="B88" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>137232435</v>
       </c>
       <c r="B89" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>137232467</v>
       </c>
       <c r="B90" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>137263435</v>
       </c>
       <c r="B91" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>137263830</v>
       </c>
       <c r="B92" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>137233307</v>
       </c>
       <c r="B93" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137254789</v>
       </c>
       <c r="B95" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233984</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137235288</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137231203</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137233141</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137261938</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137229409</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137230592</v>
       </c>
       <c r="B8" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137231226</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137231410</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137233160</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137235031</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137235205</v>
       </c>
       <c r="B13" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137254773</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137254774</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137232286</v>
       </c>
       <c r="B17" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137234103</v>
       </c>
       <c r="B18" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137233947</v>
       </c>
       <c r="B19" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137234938</v>
       </c>
       <c r="B22" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>137254772</v>
       </c>
       <c r="B24" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137229198</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>137229611</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137229946</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137230226</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137230276</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137230372</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137231296</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137231398</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137231488</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137232819</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137232846</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137233192</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137233573</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137233676</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>137261670</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>137261705</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137262560</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>137262737</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137262883</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>137262978</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>137263018</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>137264116</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137263281</v>
       </c>
       <c r="B48" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>137229855</v>
       </c>
       <c r="B55" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137231784</v>
       </c>
       <c r="B56" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137232326</v>
       </c>
       <c r="B57" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>137232603</v>
       </c>
       <c r="B58" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>137254781</v>
       </c>
       <c r="B59" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>137254782</v>
       </c>
       <c r="B60" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137263199</v>
       </c>
       <c r="B61" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137229897</v>
       </c>
       <c r="B62" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>137233252</v>
       </c>
       <c r="B63" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137234449</v>
       </c>
       <c r="B64" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>137254778</v>
       </c>
       <c r="B65" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>137234122</v>
       </c>
       <c r="B67" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>137262332</v>
       </c>
       <c r="B68" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137232378</v>
       </c>
       <c r="B69" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>137231352</v>
       </c>
       <c r="B87" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137231958</v>
       </c>
       <c r="B88" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>137232435</v>
       </c>
       <c r="B89" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>137232467</v>
       </c>
       <c r="B90" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>137263435</v>
       </c>
       <c r="B91" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>137263830</v>
       </c>
       <c r="B92" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>137233307</v>
       </c>
       <c r="B93" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137254789</v>
       </c>
       <c r="B95" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 43690-2026 artfynd.xlsx
+++ b/artfynd/A 43690-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233984</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137235288</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137231203</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137233141</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137261938</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137229409</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137230592</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137231226</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137231410</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137233160</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137235031</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137235205</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137254773</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137254774</v>
       </c>
       <c r="B15" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137232286</v>
       </c>
       <c r="B17" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137234103</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137233947</v>
       </c>
       <c r="B19" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137234938</v>
       </c>
       <c r="B22" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>137254772</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137229198</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>137229611</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137229946</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137230226</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137230276</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137230372</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137231296</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137231398</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137231488</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137232819</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137232846</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137233192</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137233573</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137233676</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>137261670</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>137261705</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137262560</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>137262737</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137262883</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>137262978</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>137263018</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>137264116</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137263281</v>
       </c>
       <c r="B48" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>137229855</v>
       </c>
       <c r="B55" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137231784</v>
       </c>
       <c r="B56" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137232326</v>
       </c>
       <c r="B57" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>137232603</v>
       </c>
       <c r="B58" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>137254781</v>
       </c>
       <c r="B59" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>137254782</v>
       </c>
       <c r="B60" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137263199</v>
       </c>
       <c r="B61" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137229897</v>
       </c>
       <c r="B62" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>137233252</v>
       </c>
       <c r="B63" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137234449</v>
       </c>
       <c r="B64" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>137254778</v>
       </c>
       <c r="B65" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>137234122</v>
       </c>
       <c r="B67" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>137262332</v>
       </c>
       <c r="B68" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137232378</v>
       </c>
       <c r="B69" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>137230795</v>
       </c>
       <c r="B70" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>137229268</v>
       </c>
       <c r="B77" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>137231851</v>
       </c>
       <c r="B78" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>137229679</v>
       </c>
       <c r="B80" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>137230147</v>
       </c>
       <c r="B83" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>137231352</v>
       </c>
       <c r="B87" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137231958</v>
       </c>
       <c r="B88" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>137232435</v>
       </c>
       <c r="B89" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>137232467</v>
       </c>
       <c r="B90" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>137263435</v>
       </c>
       <c r="B91" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>137263830</v>
       </c>
       <c r="B92" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>137233307</v>
       </c>
       <c r="B93" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137254789</v>
       </c>
       <c r="B95" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
